--- a/artfynd/A 54736-2023 artfynd.xlsx
+++ b/artfynd/A 54736-2023 artfynd.xlsx
@@ -2640,10 +2640,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118420695</v>
+        <v>118420091</v>
       </c>
       <c r="B20" t="n">
-        <v>100124</v>
+        <v>78484</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2652,25 +2652,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1853</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mosippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pulsatilla vernalis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2680,10 +2680,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>388483</v>
+        <v>388686</v>
       </c>
       <c r="R20" t="n">
-        <v>6844565</v>
+        <v>6844618</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2726,6 +2726,26 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2844,10 +2864,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118420091</v>
+        <v>118420695</v>
       </c>
       <c r="B22" t="n">
-        <v>78484</v>
+        <v>100124</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2856,25 +2876,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1853</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mosippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pulsatilla vernalis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2884,10 +2904,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>388686</v>
+        <v>388483</v>
       </c>
       <c r="R22" t="n">
-        <v>6844618</v>
+        <v>6844565</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2930,26 +2950,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">

--- a/artfynd/A 54736-2023 artfynd.xlsx
+++ b/artfynd/A 54736-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118420814</v>
+        <v>118418584</v>
       </c>
       <c r="B2" t="n">
-        <v>78220</v>
+        <v>90654</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>1503</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>388469</v>
+        <v>388595</v>
       </c>
       <c r="R2" t="n">
-        <v>6844519</v>
+        <v>6844385</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -761,6 +761,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -777,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118420560</v>
+        <v>118419412</v>
       </c>
       <c r="B3" t="n">
-        <v>78220</v>
+        <v>78484</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +813,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>388466</v>
+        <v>388803</v>
       </c>
       <c r="R3" t="n">
-        <v>6844600</v>
+        <v>6844256</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -863,6 +883,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -879,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118421034</v>
+        <v>118420637</v>
       </c>
       <c r="B4" t="n">
-        <v>91779</v>
+        <v>100124</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,38 +931,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>1853</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mosippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pulsatilla vernalis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Västanberget (Västanberget), Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>388505</v>
+        <v>388471</v>
       </c>
       <c r="R4" t="n">
-        <v>6844252</v>
+        <v>6844575</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118420824</v>
+        <v>118420773</v>
       </c>
       <c r="B5" t="n">
-        <v>78221</v>
+        <v>100124</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +1042,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>1853</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mosippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Pulsatilla vernalis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1070,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>388469</v>
+        <v>388501</v>
       </c>
       <c r="R5" t="n">
-        <v>6844519</v>
+        <v>6844507</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118420061</v>
+        <v>118421034</v>
       </c>
       <c r="B6" t="n">
-        <v>78484</v>
+        <v>91779</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1144,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1172,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>388644</v>
+        <v>388505</v>
       </c>
       <c r="R6" t="n">
-        <v>6844604</v>
+        <v>6844252</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,26 +1218,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1205,10 +1234,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118419304</v>
+        <v>118420061</v>
       </c>
       <c r="B7" t="n">
-        <v>95394</v>
+        <v>78484</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1250,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>388802</v>
+        <v>388644</v>
       </c>
       <c r="R7" t="n">
-        <v>6844204</v>
+        <v>6844604</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1291,6 +1320,26 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1307,10 +1356,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118419526</v>
+        <v>118420091</v>
       </c>
       <c r="B8" t="n">
-        <v>78221</v>
+        <v>78484</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,21 +1372,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1396,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>388784</v>
+        <v>388686</v>
       </c>
       <c r="R8" t="n">
-        <v>6844286</v>
+        <v>6844618</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1393,6 +1442,26 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1409,10 +1478,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118420773</v>
+        <v>118419304</v>
       </c>
       <c r="B9" t="n">
-        <v>100124</v>
+        <v>95394</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1421,25 +1490,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1853</v>
+        <v>53</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mosippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pulsatilla vernalis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1518,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>388501</v>
+        <v>388802</v>
       </c>
       <c r="R9" t="n">
-        <v>6844507</v>
+        <v>6844204</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1511,10 +1580,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118419640</v>
+        <v>118420560</v>
       </c>
       <c r="B10" t="n">
-        <v>79073</v>
+        <v>78220</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1527,21 +1596,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1551,10 +1620,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>388768</v>
+        <v>388466</v>
       </c>
       <c r="R10" t="n">
-        <v>6844285</v>
+        <v>6844600</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,26 +1666,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1633,10 +1682,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118420972</v>
+        <v>118419758</v>
       </c>
       <c r="B11" t="n">
-        <v>79073</v>
+        <v>95394</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1649,21 +1698,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229821</v>
+        <v>53</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1722,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>388469</v>
+        <v>388735</v>
       </c>
       <c r="R11" t="n">
-        <v>6844519</v>
+        <v>6844323</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1784,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118419669</v>
+        <v>118418751</v>
       </c>
       <c r="B12" t="n">
-        <v>100124</v>
+        <v>95394</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1747,25 +1796,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1853</v>
+        <v>53</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mosippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pulsatilla vernalis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1824,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>388753</v>
+        <v>388594</v>
       </c>
       <c r="R12" t="n">
-        <v>6844306</v>
+        <v>6844349</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1821,6 +1870,26 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1837,10 +1906,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118419758</v>
+        <v>118418878</v>
       </c>
       <c r="B13" t="n">
-        <v>95394</v>
+        <v>79102</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,21 +1922,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>53</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1877,10 +1946,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>388735</v>
+        <v>388660</v>
       </c>
       <c r="R13" t="n">
-        <v>6844323</v>
+        <v>6844317</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1923,6 +1992,26 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -1939,10 +2028,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118418584</v>
+        <v>118419640</v>
       </c>
       <c r="B14" t="n">
-        <v>90654</v>
+        <v>79073</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1951,25 +2040,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1503</v>
+        <v>229821</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1979,10 +2068,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>388595</v>
+        <v>388768</v>
       </c>
       <c r="R14" t="n">
-        <v>6844385</v>
+        <v>6844285</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2038,12 +2127,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Vedyta på död ved</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2061,10 +2150,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118419164</v>
+        <v>118420695</v>
       </c>
       <c r="B15" t="n">
-        <v>79102</v>
+        <v>100124</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2073,25 +2162,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>1853</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mosippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pulsatilla vernalis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2101,10 +2190,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>388677</v>
+        <v>388483</v>
       </c>
       <c r="R15" t="n">
-        <v>6844240</v>
+        <v>6844565</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2163,10 +2252,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118420637</v>
+        <v>118419458</v>
       </c>
       <c r="B16" t="n">
-        <v>100124</v>
+        <v>79102</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2175,47 +2264,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1853</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mosippa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pulsatilla vernalis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Västanberget (Västanberget), Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>388471</v>
+        <v>388790</v>
       </c>
       <c r="R16" t="n">
-        <v>6844575</v>
+        <v>6844263</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2274,10 +2354,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118420743</v>
+        <v>118419164</v>
       </c>
       <c r="B17" t="n">
-        <v>78583</v>
+        <v>79102</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2290,21 +2370,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>967</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2314,10 +2394,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>388502</v>
+        <v>388677</v>
       </c>
       <c r="R17" t="n">
-        <v>6844522</v>
+        <v>6844240</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2360,26 +2440,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2396,10 +2456,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118419412</v>
+        <v>118420824</v>
       </c>
       <c r="B18" t="n">
-        <v>78484</v>
+        <v>78221</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2412,21 +2472,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2436,10 +2496,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>388803</v>
+        <v>388469</v>
       </c>
       <c r="R18" t="n">
-        <v>6844256</v>
+        <v>6844519</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2482,26 +2542,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2518,10 +2558,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118420490</v>
+        <v>118419240</v>
       </c>
       <c r="B19" t="n">
-        <v>90430</v>
+        <v>79102</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2534,21 +2574,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3242</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2558,10 +2598,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>388468</v>
+        <v>388763</v>
       </c>
       <c r="R19" t="n">
-        <v>6844616</v>
+        <v>6844188</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2604,26 +2644,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2640,10 +2660,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118420091</v>
+        <v>118419526</v>
       </c>
       <c r="B20" t="n">
-        <v>78484</v>
+        <v>78221</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2656,21 +2676,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2680,10 +2700,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>388686</v>
+        <v>388784</v>
       </c>
       <c r="R20" t="n">
-        <v>6844618</v>
+        <v>6844286</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2726,26 +2746,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2762,10 +2762,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118419240</v>
+        <v>118420723</v>
       </c>
       <c r="B21" t="n">
-        <v>79102</v>
+        <v>100124</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2774,38 +2774,47 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>1853</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mosippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pulsatilla vernalis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Västanberget (Västanberget), Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>388763</v>
+        <v>388503</v>
       </c>
       <c r="R21" t="n">
-        <v>6844188</v>
+        <v>6844553</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2864,10 +2873,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118420695</v>
+        <v>118420972</v>
       </c>
       <c r="B22" t="n">
-        <v>100124</v>
+        <v>79073</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2876,25 +2885,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1853</v>
+        <v>229821</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mosippa</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pulsatilla vernalis</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2904,10 +2913,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>388483</v>
+        <v>388469</v>
       </c>
       <c r="R22" t="n">
-        <v>6844565</v>
+        <v>6844519</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2966,7 +2975,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118420723</v>
+        <v>118419669</v>
       </c>
       <c r="B23" t="n">
         <v>100124</v>
@@ -2999,26 +3008,17 @@
           <t>(L.) Mill.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Västanberget (Västanberget), Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>388503</v>
+        <v>388753</v>
       </c>
       <c r="R23" t="n">
-        <v>6844553</v>
+        <v>6844306</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3077,10 +3077,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118419451</v>
+        <v>118420275</v>
       </c>
       <c r="B24" t="n">
-        <v>78220</v>
+        <v>78484</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3093,21 +3093,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3117,10 +3117,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>388790</v>
+        <v>388584</v>
       </c>
       <c r="R24" t="n">
-        <v>6844263</v>
+        <v>6844653</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3163,6 +3163,26 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3179,10 +3199,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118420275</v>
+        <v>118419050</v>
       </c>
       <c r="B25" t="n">
-        <v>78484</v>
+        <v>100124</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3191,25 +3211,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1853</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mosippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pulsatilla vernalis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3219,10 +3239,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>388584</v>
+        <v>388692</v>
       </c>
       <c r="R25" t="n">
-        <v>6844653</v>
+        <v>6844280</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3265,26 +3285,6 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3301,10 +3301,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118419050</v>
+        <v>118420743</v>
       </c>
       <c r="B26" t="n">
-        <v>100124</v>
+        <v>78583</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3313,25 +3313,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1853</v>
+        <v>967</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mosippa</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pulsatilla vernalis</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3341,10 +3341,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>388692</v>
+        <v>388502</v>
       </c>
       <c r="R26" t="n">
-        <v>6844280</v>
+        <v>6844522</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3387,6 +3387,26 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3403,10 +3423,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118418751</v>
+        <v>118420814</v>
       </c>
       <c r="B27" t="n">
-        <v>95394</v>
+        <v>78220</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3419,21 +3439,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>53</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3443,10 +3463,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>388594</v>
+        <v>388469</v>
       </c>
       <c r="R27" t="n">
-        <v>6844349</v>
+        <v>6844519</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3489,26 +3509,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3525,10 +3525,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118420182</v>
+        <v>118420490</v>
       </c>
       <c r="B28" t="n">
-        <v>78484</v>
+        <v>90430</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3541,21 +3541,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>3242</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3565,10 +3565,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>388647</v>
+        <v>388468</v>
       </c>
       <c r="R28" t="n">
-        <v>6844639</v>
+        <v>6844616</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3614,22 +3614,22 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3647,10 +3647,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118419458</v>
+        <v>118420182</v>
       </c>
       <c r="B29" t="n">
-        <v>79102</v>
+        <v>78484</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3663,21 +3663,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3687,10 +3687,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>388790</v>
+        <v>388647</v>
       </c>
       <c r="R29" t="n">
-        <v>6844263</v>
+        <v>6844639</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3733,6 +3733,26 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3749,10 +3769,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118418878</v>
+        <v>118419451</v>
       </c>
       <c r="B30" t="n">
-        <v>79102</v>
+        <v>78220</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3765,21 +3785,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3789,10 +3809,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>388660</v>
+        <v>388790</v>
       </c>
       <c r="R30" t="n">
-        <v>6844317</v>
+        <v>6844263</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3835,26 +3855,6 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">

--- a/artfynd/A 54736-2023 artfynd.xlsx
+++ b/artfynd/A 54736-2023 artfynd.xlsx
@@ -2873,10 +2873,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118420972</v>
+        <v>118419669</v>
       </c>
       <c r="B22" t="n">
-        <v>79073</v>
+        <v>100124</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2885,25 +2885,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229821</v>
+        <v>1853</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mosippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Pulsatilla vernalis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2913,10 +2913,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>388469</v>
+        <v>388753</v>
       </c>
       <c r="R22" t="n">
-        <v>6844519</v>
+        <v>6844306</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2975,10 +2975,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118419669</v>
+        <v>118420972</v>
       </c>
       <c r="B23" t="n">
-        <v>100124</v>
+        <v>79073</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2987,25 +2987,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1853</v>
+        <v>229821</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mosippa</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pulsatilla vernalis</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3015,10 +3015,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>388753</v>
+        <v>388469</v>
       </c>
       <c r="R23" t="n">
-        <v>6844306</v>
+        <v>6844519</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 54736-2023 artfynd.xlsx
+++ b/artfynd/A 54736-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118418584</v>
+        <v>118420490</v>
       </c>
       <c r="B2" t="n">
-        <v>90654</v>
+        <v>90430</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1503</v>
+        <v>3242</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>388595</v>
+        <v>388468</v>
       </c>
       <c r="R2" t="n">
-        <v>6844385</v>
+        <v>6844616</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -774,12 +774,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+          <t>Horizontal, dead without ground contact # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -797,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118419412</v>
+        <v>118419758</v>
       </c>
       <c r="B3" t="n">
-        <v>78484</v>
+        <v>95394</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,21 +813,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>388803</v>
+        <v>388735</v>
       </c>
       <c r="R3" t="n">
-        <v>6844256</v>
+        <v>6844323</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -883,26 +883,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -919,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118420637</v>
+        <v>118420723</v>
       </c>
       <c r="B4" t="n">
         <v>100124</v>
@@ -954,7 +934,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -968,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>388471</v>
+        <v>388503</v>
       </c>
       <c r="R4" t="n">
-        <v>6844575</v>
+        <v>6844553</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1030,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118420773</v>
+        <v>118419164</v>
       </c>
       <c r="B5" t="n">
-        <v>100124</v>
+        <v>79102</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,25 +1022,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1853</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mosippa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pulsatilla vernalis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1070,10 +1050,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>388501</v>
+        <v>388677</v>
       </c>
       <c r="R5" t="n">
-        <v>6844507</v>
+        <v>6844240</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1132,10 +1112,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118421034</v>
+        <v>118419640</v>
       </c>
       <c r="B6" t="n">
-        <v>91779</v>
+        <v>79073</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,25 +1124,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1172,10 +1152,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>388505</v>
+        <v>388768</v>
       </c>
       <c r="R6" t="n">
-        <v>6844252</v>
+        <v>6844285</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,6 +1198,26 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1234,10 +1234,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118420061</v>
+        <v>118420773</v>
       </c>
       <c r="B7" t="n">
-        <v>78484</v>
+        <v>100124</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,25 +1246,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1853</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mosippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pulsatilla vernalis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>388644</v>
+        <v>388501</v>
       </c>
       <c r="R7" t="n">
-        <v>6844604</v>
+        <v>6844507</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1320,26 +1320,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1356,10 +1336,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118420091</v>
+        <v>118419526</v>
       </c>
       <c r="B8" t="n">
-        <v>78484</v>
+        <v>78221</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1372,21 +1352,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1396,10 +1376,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>388686</v>
+        <v>388784</v>
       </c>
       <c r="R8" t="n">
-        <v>6844618</v>
+        <v>6844286</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1442,26 +1422,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1478,10 +1438,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118419304</v>
+        <v>118419458</v>
       </c>
       <c r="B9" t="n">
-        <v>95394</v>
+        <v>79102</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1494,21 +1454,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1518,10 +1478,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>388802</v>
+        <v>388790</v>
       </c>
       <c r="R9" t="n">
-        <v>6844204</v>
+        <v>6844263</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1580,10 +1540,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118420560</v>
+        <v>118420743</v>
       </c>
       <c r="B10" t="n">
-        <v>78220</v>
+        <v>78583</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1596,21 +1556,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>967</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1620,10 +1580,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>388466</v>
+        <v>388502</v>
       </c>
       <c r="R10" t="n">
-        <v>6844600</v>
+        <v>6844522</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1666,6 +1626,26 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1682,10 +1662,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118419758</v>
+        <v>118418584</v>
       </c>
       <c r="B11" t="n">
-        <v>95394</v>
+        <v>90654</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1694,25 +1674,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>1503</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1722,10 +1702,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>388735</v>
+        <v>388595</v>
       </c>
       <c r="R11" t="n">
-        <v>6844323</v>
+        <v>6844385</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1768,6 +1748,26 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1784,10 +1784,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118418751</v>
+        <v>118420560</v>
       </c>
       <c r="B12" t="n">
-        <v>95394</v>
+        <v>78220</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1800,21 +1800,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1824,10 +1824,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>388594</v>
+        <v>388466</v>
       </c>
       <c r="R12" t="n">
-        <v>6844349</v>
+        <v>6844600</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1870,26 +1870,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1906,10 +1886,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118418878</v>
+        <v>118419412</v>
       </c>
       <c r="B13" t="n">
-        <v>79102</v>
+        <v>78484</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1922,21 +1902,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1946,10 +1926,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>388660</v>
+        <v>388803</v>
       </c>
       <c r="R13" t="n">
-        <v>6844317</v>
+        <v>6844256</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2005,12 +1985,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Vedyta på död ved</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
+          <t>Branch on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2028,10 +2008,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118419640</v>
+        <v>118420091</v>
       </c>
       <c r="B14" t="n">
-        <v>79073</v>
+        <v>78484</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2044,21 +2024,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2068,10 +2048,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>388768</v>
+        <v>388686</v>
       </c>
       <c r="R14" t="n">
-        <v>6844285</v>
+        <v>6844618</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2117,22 +2097,22 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Vedyta på död ved</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2252,10 +2232,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118419458</v>
+        <v>118420637</v>
       </c>
       <c r="B16" t="n">
-        <v>79102</v>
+        <v>100124</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2264,38 +2244,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>1853</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mosippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pulsatilla vernalis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Västanberget (Västanberget), Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>388790</v>
+        <v>388471</v>
       </c>
       <c r="R16" t="n">
-        <v>6844263</v>
+        <v>6844575</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2354,10 +2343,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118419164</v>
+        <v>118421034</v>
       </c>
       <c r="B17" t="n">
-        <v>79102</v>
+        <v>91779</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2366,25 +2355,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2394,10 +2383,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>388677</v>
+        <v>388505</v>
       </c>
       <c r="R17" t="n">
-        <v>6844240</v>
+        <v>6844252</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2456,10 +2445,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118420824</v>
+        <v>118420061</v>
       </c>
       <c r="B18" t="n">
-        <v>78221</v>
+        <v>78484</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2472,21 +2461,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2496,10 +2485,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>388469</v>
+        <v>388644</v>
       </c>
       <c r="R18" t="n">
-        <v>6844519</v>
+        <v>6844604</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2542,6 +2531,26 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2558,10 +2567,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118419240</v>
+        <v>118419304</v>
       </c>
       <c r="B19" t="n">
-        <v>79102</v>
+        <v>95394</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2574,21 +2583,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>53</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2598,10 +2607,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>388763</v>
+        <v>388802</v>
       </c>
       <c r="R19" t="n">
-        <v>6844188</v>
+        <v>6844204</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2660,10 +2669,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118419526</v>
+        <v>118420182</v>
       </c>
       <c r="B20" t="n">
-        <v>78221</v>
+        <v>78484</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2676,21 +2685,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2700,10 +2709,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>388784</v>
+        <v>388647</v>
       </c>
       <c r="R20" t="n">
-        <v>6844286</v>
+        <v>6844639</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2746,6 +2755,26 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2762,10 +2791,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118420723</v>
+        <v>118419451</v>
       </c>
       <c r="B21" t="n">
-        <v>100124</v>
+        <v>78220</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2774,47 +2803,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1853</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mosippa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pulsatilla vernalis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Västanberget (Västanberget), Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>388503</v>
+        <v>388790</v>
       </c>
       <c r="R21" t="n">
-        <v>6844553</v>
+        <v>6844263</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2873,10 +2893,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118419669</v>
+        <v>118420275</v>
       </c>
       <c r="B22" t="n">
-        <v>100124</v>
+        <v>78484</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2885,25 +2905,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1853</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mosippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pulsatilla vernalis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2913,10 +2933,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>388753</v>
+        <v>388584</v>
       </c>
       <c r="R22" t="n">
-        <v>6844306</v>
+        <v>6844653</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2959,6 +2979,26 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -2975,10 +3015,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118420972</v>
+        <v>118418751</v>
       </c>
       <c r="B23" t="n">
-        <v>79073</v>
+        <v>95394</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2991,21 +3031,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229821</v>
+        <v>53</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3015,10 +3055,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>388469</v>
+        <v>388594</v>
       </c>
       <c r="R23" t="n">
-        <v>6844519</v>
+        <v>6844349</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3061,6 +3101,26 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3077,10 +3137,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118420275</v>
+        <v>118419240</v>
       </c>
       <c r="B24" t="n">
-        <v>78484</v>
+        <v>79102</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3093,21 +3153,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3117,10 +3177,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>388584</v>
+        <v>388763</v>
       </c>
       <c r="R24" t="n">
-        <v>6844653</v>
+        <v>6844188</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3163,26 +3223,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3199,10 +3239,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118419050</v>
+        <v>118418878</v>
       </c>
       <c r="B25" t="n">
-        <v>100124</v>
+        <v>79102</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3211,25 +3251,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1853</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mosippa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pulsatilla vernalis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3239,10 +3279,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>388692</v>
+        <v>388660</v>
       </c>
       <c r="R25" t="n">
-        <v>6844280</v>
+        <v>6844317</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3285,6 +3325,26 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3301,10 +3361,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118420743</v>
+        <v>118420972</v>
       </c>
       <c r="B26" t="n">
-        <v>78583</v>
+        <v>79073</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3317,21 +3377,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>967</v>
+        <v>229821</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3341,10 +3401,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>388502</v>
+        <v>388469</v>
       </c>
       <c r="R26" t="n">
-        <v>6844522</v>
+        <v>6844519</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3387,26 +3447,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3423,10 +3463,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118420814</v>
+        <v>118420824</v>
       </c>
       <c r="B27" t="n">
-        <v>78220</v>
+        <v>78221</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3439,21 +3479,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3525,10 +3565,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118420490</v>
+        <v>118419669</v>
       </c>
       <c r="B28" t="n">
-        <v>90430</v>
+        <v>100124</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3537,25 +3577,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3242</v>
+        <v>1853</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Mosippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Pulsatilla vernalis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3565,10 +3605,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>388468</v>
+        <v>388753</v>
       </c>
       <c r="R28" t="n">
-        <v>6844616</v>
+        <v>6844306</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3611,26 +3651,6 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3647,10 +3667,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118420182</v>
+        <v>118419050</v>
       </c>
       <c r="B29" t="n">
-        <v>78484</v>
+        <v>100124</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3659,25 +3679,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1853</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mosippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pulsatilla vernalis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3687,10 +3707,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>388647</v>
+        <v>388692</v>
       </c>
       <c r="R29" t="n">
-        <v>6844639</v>
+        <v>6844280</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3733,26 +3753,6 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3769,7 +3769,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118419451</v>
+        <v>118420814</v>
       </c>
       <c r="B30" t="n">
         <v>78220</v>
@@ -3809,10 +3809,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>388790</v>
+        <v>388469</v>
       </c>
       <c r="R30" t="n">
-        <v>6844263</v>
+        <v>6844519</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 54736-2023 artfynd.xlsx
+++ b/artfynd/A 54736-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118420490</v>
+        <v>118419640</v>
       </c>
       <c r="B2" t="n">
-        <v>90430</v>
+        <v>79080</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3242</v>
+        <v>229821</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>388468</v>
+        <v>388768</v>
       </c>
       <c r="R2" t="n">
-        <v>6844616</v>
+        <v>6844285</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -774,12 +774,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Vedyta på död ved</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Pinus sylvestris</t>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -797,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118419758</v>
+        <v>118420743</v>
       </c>
       <c r="B3" t="n">
-        <v>95394</v>
+        <v>78590</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,21 +813,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>967</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>388735</v>
+        <v>388502</v>
       </c>
       <c r="R3" t="n">
-        <v>6844323</v>
+        <v>6844522</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -883,6 +883,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -899,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118420723</v>
+        <v>118418584</v>
       </c>
       <c r="B4" t="n">
-        <v>100124</v>
+        <v>90661</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,47 +931,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1853</v>
+        <v>1503</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mosippa</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pulsatilla vernalis</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Västanberget (Västanberget), Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>388503</v>
+        <v>388595</v>
       </c>
       <c r="R4" t="n">
-        <v>6844553</v>
+        <v>6844385</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,6 +1005,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1010,10 +1041,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118419164</v>
+        <v>118421034</v>
       </c>
       <c r="B5" t="n">
-        <v>79102</v>
+        <v>91786</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,25 +1053,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1050,10 +1081,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>388677</v>
+        <v>388505</v>
       </c>
       <c r="R5" t="n">
-        <v>6844240</v>
+        <v>6844252</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1112,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118419640</v>
+        <v>118419240</v>
       </c>
       <c r="B6" t="n">
-        <v>79073</v>
+        <v>79109</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1128,21 +1159,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1152,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>388768</v>
+        <v>388763</v>
       </c>
       <c r="R6" t="n">
-        <v>6844285</v>
+        <v>6844188</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,26 +1229,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1234,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118420773</v>
+        <v>118419758</v>
       </c>
       <c r="B7" t="n">
-        <v>100124</v>
+        <v>95401</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,25 +1257,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1853</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mosippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pulsatilla vernalis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1274,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>388501</v>
+        <v>388735</v>
       </c>
       <c r="R7" t="n">
-        <v>6844507</v>
+        <v>6844323</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1336,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118419526</v>
+        <v>118420182</v>
       </c>
       <c r="B8" t="n">
-        <v>78221</v>
+        <v>78491</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1352,21 +1363,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1376,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>388784</v>
+        <v>388647</v>
       </c>
       <c r="R8" t="n">
-        <v>6844286</v>
+        <v>6844639</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,6 +1433,26 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1438,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118419458</v>
+        <v>118419304</v>
       </c>
       <c r="B9" t="n">
-        <v>79102</v>
+        <v>95401</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1454,21 +1485,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>53</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1478,10 +1509,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>388790</v>
+        <v>388802</v>
       </c>
       <c r="R9" t="n">
-        <v>6844263</v>
+        <v>6844204</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1540,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118420743</v>
+        <v>118419412</v>
       </c>
       <c r="B10" t="n">
-        <v>78583</v>
+        <v>78491</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1556,21 +1587,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>967</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1580,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>388502</v>
+        <v>388803</v>
       </c>
       <c r="R10" t="n">
-        <v>6844522</v>
+        <v>6844256</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1639,12 +1670,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Vedyta på död ved</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
+          <t>Branch on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1662,10 +1693,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118418584</v>
+        <v>118420824</v>
       </c>
       <c r="B11" t="n">
-        <v>90654</v>
+        <v>78228</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1674,25 +1705,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1702,10 +1733,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>388595</v>
+        <v>388469</v>
       </c>
       <c r="R11" t="n">
-        <v>6844385</v>
+        <v>6844519</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1748,26 +1779,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1784,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118420560</v>
+        <v>118418878</v>
       </c>
       <c r="B12" t="n">
-        <v>78220</v>
+        <v>79109</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1800,21 +1811,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1824,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>388466</v>
+        <v>388660</v>
       </c>
       <c r="R12" t="n">
-        <v>6844600</v>
+        <v>6844317</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1870,6 +1881,26 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1886,10 +1917,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118419412</v>
+        <v>118420091</v>
       </c>
       <c r="B13" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1926,10 +1957,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>388803</v>
+        <v>388686</v>
       </c>
       <c r="R13" t="n">
-        <v>6844256</v>
+        <v>6844618</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1975,12 +2006,12 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -1990,7 +2021,7 @@
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Branch on living tree # Pinus sylvestris</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2008,10 +2039,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118420091</v>
+        <v>118420061</v>
       </c>
       <c r="B14" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2048,10 +2079,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>388686</v>
+        <v>388644</v>
       </c>
       <c r="R14" t="n">
-        <v>6844618</v>
+        <v>6844604</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2097,12 +2128,12 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -2112,7 +2143,7 @@
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Branch on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2130,10 +2161,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118420695</v>
+        <v>118419526</v>
       </c>
       <c r="B15" t="n">
-        <v>100124</v>
+        <v>78228</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2142,25 +2173,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1853</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mosippa</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pulsatilla vernalis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2170,10 +2201,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>388483</v>
+        <v>388784</v>
       </c>
       <c r="R15" t="n">
-        <v>6844565</v>
+        <v>6844286</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2235,7 +2266,7 @@
         <v>118420637</v>
       </c>
       <c r="B16" t="n">
-        <v>100124</v>
+        <v>100131</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2343,10 +2374,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118421034</v>
+        <v>118419458</v>
       </c>
       <c r="B17" t="n">
-        <v>91779</v>
+        <v>79109</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2355,25 +2386,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2383,10 +2414,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>388505</v>
+        <v>388790</v>
       </c>
       <c r="R17" t="n">
-        <v>6844252</v>
+        <v>6844263</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2445,10 +2476,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118420061</v>
+        <v>118419164</v>
       </c>
       <c r="B18" t="n">
-        <v>78484</v>
+        <v>79109</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2461,21 +2492,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2485,10 +2516,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>388644</v>
+        <v>388677</v>
       </c>
       <c r="R18" t="n">
-        <v>6844604</v>
+        <v>6844240</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2531,26 +2562,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2567,10 +2578,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118419304</v>
+        <v>118420275</v>
       </c>
       <c r="B19" t="n">
-        <v>95394</v>
+        <v>78491</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2583,21 +2594,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2607,10 +2618,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>388802</v>
+        <v>388584</v>
       </c>
       <c r="R19" t="n">
-        <v>6844204</v>
+        <v>6844653</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2653,6 +2664,26 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2669,10 +2700,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118420182</v>
+        <v>118420723</v>
       </c>
       <c r="B20" t="n">
-        <v>78484</v>
+        <v>100131</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2681,38 +2712,47 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1853</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mosippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pulsatilla vernalis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Västanberget (Västanberget), Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>388647</v>
+        <v>388503</v>
       </c>
       <c r="R20" t="n">
-        <v>6844639</v>
+        <v>6844553</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2755,26 +2795,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2791,10 +2811,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118419451</v>
+        <v>118420490</v>
       </c>
       <c r="B21" t="n">
-        <v>78220</v>
+        <v>90437</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2807,21 +2827,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>3242</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2831,10 +2851,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>388790</v>
+        <v>388468</v>
       </c>
       <c r="R21" t="n">
-        <v>6844263</v>
+        <v>6844616</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2877,6 +2897,26 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2893,10 +2933,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118420275</v>
+        <v>118419669</v>
       </c>
       <c r="B22" t="n">
-        <v>78484</v>
+        <v>100131</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2905,25 +2945,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1853</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mosippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pulsatilla vernalis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2933,10 +2973,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>388584</v>
+        <v>388753</v>
       </c>
       <c r="R22" t="n">
-        <v>6844653</v>
+        <v>6844306</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2979,26 +3019,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3015,10 +3035,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118418751</v>
+        <v>118419050</v>
       </c>
       <c r="B23" t="n">
-        <v>95394</v>
+        <v>100131</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3027,25 +3047,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>53</v>
+        <v>1853</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mosippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pulsatilla vernalis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3055,10 +3075,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>388594</v>
+        <v>388692</v>
       </c>
       <c r="R23" t="n">
-        <v>6844349</v>
+        <v>6844280</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3101,26 +3121,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3137,10 +3137,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118419240</v>
+        <v>118420560</v>
       </c>
       <c r="B24" t="n">
-        <v>79102</v>
+        <v>78227</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3153,21 +3153,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3177,10 +3177,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>388763</v>
+        <v>388466</v>
       </c>
       <c r="R24" t="n">
-        <v>6844188</v>
+        <v>6844600</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3239,10 +3239,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118418878</v>
+        <v>118420814</v>
       </c>
       <c r="B25" t="n">
-        <v>79102</v>
+        <v>78227</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3255,21 +3255,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3279,10 +3279,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>388660</v>
+        <v>388469</v>
       </c>
       <c r="R25" t="n">
-        <v>6844317</v>
+        <v>6844519</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3325,26 +3325,6 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3364,7 +3344,7 @@
         <v>118420972</v>
       </c>
       <c r="B26" t="n">
-        <v>79073</v>
+        <v>79080</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3463,10 +3443,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118420824</v>
+        <v>118420695</v>
       </c>
       <c r="B27" t="n">
-        <v>78221</v>
+        <v>100131</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3475,25 +3455,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>1853</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mosippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Pulsatilla vernalis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3503,10 +3483,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>388469</v>
+        <v>388483</v>
       </c>
       <c r="R27" t="n">
-        <v>6844519</v>
+        <v>6844565</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3565,10 +3545,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118419669</v>
+        <v>118420773</v>
       </c>
       <c r="B28" t="n">
-        <v>100124</v>
+        <v>100131</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3605,10 +3585,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>388753</v>
+        <v>388501</v>
       </c>
       <c r="R28" t="n">
-        <v>6844306</v>
+        <v>6844507</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3667,10 +3647,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118419050</v>
+        <v>118419451</v>
       </c>
       <c r="B29" t="n">
-        <v>100124</v>
+        <v>78227</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3679,25 +3659,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1853</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mosippa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pulsatilla vernalis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3707,10 +3687,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>388692</v>
+        <v>388790</v>
       </c>
       <c r="R29" t="n">
-        <v>6844280</v>
+        <v>6844263</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3769,10 +3749,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118420814</v>
+        <v>118418751</v>
       </c>
       <c r="B30" t="n">
-        <v>78220</v>
+        <v>95401</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3785,21 +3765,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>53</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3809,10 +3789,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>388469</v>
+        <v>388594</v>
       </c>
       <c r="R30" t="n">
-        <v>6844519</v>
+        <v>6844349</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3855,6 +3835,26 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">

--- a/artfynd/A 54736-2023 artfynd.xlsx
+++ b/artfynd/A 54736-2023 artfynd.xlsx
@@ -1245,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118419758</v>
+        <v>118420182</v>
       </c>
       <c r="B7" t="n">
-        <v>95401</v>
+        <v>78491</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,21 +1261,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>388735</v>
+        <v>388647</v>
       </c>
       <c r="R7" t="n">
-        <v>6844323</v>
+        <v>6844639</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1331,6 +1331,26 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1347,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118420182</v>
+        <v>118419758</v>
       </c>
       <c r="B8" t="n">
-        <v>78491</v>
+        <v>95401</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,21 +1383,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1407,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>388647</v>
+        <v>388735</v>
       </c>
       <c r="R8" t="n">
-        <v>6844639</v>
+        <v>6844323</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1433,26 +1453,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -3341,10 +3341,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118420972</v>
+        <v>118420695</v>
       </c>
       <c r="B26" t="n">
-        <v>79080</v>
+        <v>100131</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3353,25 +3353,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229821</v>
+        <v>1853</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mosippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Pulsatilla vernalis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3381,10 +3381,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>388469</v>
+        <v>388483</v>
       </c>
       <c r="R26" t="n">
-        <v>6844519</v>
+        <v>6844565</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3443,10 +3443,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118420695</v>
+        <v>118420972</v>
       </c>
       <c r="B27" t="n">
-        <v>100131</v>
+        <v>79080</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3455,25 +3455,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1853</v>
+        <v>229821</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mosippa</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pulsatilla vernalis</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3483,10 +3483,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>388483</v>
+        <v>388469</v>
       </c>
       <c r="R27" t="n">
-        <v>6844565</v>
+        <v>6844519</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 54736-2023 artfynd.xlsx
+++ b/artfynd/A 54736-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118419640</v>
+        <v>118420695</v>
       </c>
       <c r="B2" t="n">
-        <v>79080</v>
+        <v>100131</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>1853</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mosippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Pulsatilla vernalis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>388768</v>
+        <v>388483</v>
       </c>
       <c r="R2" t="n">
-        <v>6844285</v>
+        <v>6844565</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -761,26 +761,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -919,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118418584</v>
+        <v>118418751</v>
       </c>
       <c r="B4" t="n">
-        <v>90661</v>
+        <v>95401</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1503</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -959,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>388595</v>
+        <v>388594</v>
       </c>
       <c r="R4" t="n">
-        <v>6844385</v>
+        <v>6844349</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1041,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118421034</v>
+        <v>118419240</v>
       </c>
       <c r="B5" t="n">
-        <v>91786</v>
+        <v>79109</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1053,25 +1033,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1081,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>388505</v>
+        <v>388763</v>
       </c>
       <c r="R5" t="n">
-        <v>6844252</v>
+        <v>6844188</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1143,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118419240</v>
+        <v>118419758</v>
       </c>
       <c r="B6" t="n">
-        <v>79109</v>
+        <v>95401</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1183,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>388763</v>
+        <v>388735</v>
       </c>
       <c r="R6" t="n">
-        <v>6844188</v>
+        <v>6844323</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1245,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118420182</v>
+        <v>118419164</v>
       </c>
       <c r="B7" t="n">
-        <v>78491</v>
+        <v>79109</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,21 +1241,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1285,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>388647</v>
+        <v>388677</v>
       </c>
       <c r="R7" t="n">
-        <v>6844639</v>
+        <v>6844240</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1331,26 +1311,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1367,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118419758</v>
+        <v>118420275</v>
       </c>
       <c r="B8" t="n">
-        <v>95401</v>
+        <v>78491</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,21 +1343,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1407,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>388735</v>
+        <v>388584</v>
       </c>
       <c r="R8" t="n">
-        <v>6844323</v>
+        <v>6844653</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1453,6 +1413,26 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1469,10 +1449,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118419304</v>
+        <v>118420972</v>
       </c>
       <c r="B9" t="n">
-        <v>95401</v>
+        <v>79080</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1485,21 +1465,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>229821</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1509,10 +1489,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>388802</v>
+        <v>388469</v>
       </c>
       <c r="R9" t="n">
-        <v>6844204</v>
+        <v>6844519</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1571,10 +1551,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118419412</v>
+        <v>118420723</v>
       </c>
       <c r="B10" t="n">
-        <v>78491</v>
+        <v>100131</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1583,38 +1563,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1853</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mosippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pulsatilla vernalis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Västanberget (Västanberget), Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>388803</v>
+        <v>388503</v>
       </c>
       <c r="R10" t="n">
-        <v>6844256</v>
+        <v>6844553</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1657,26 +1646,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1693,10 +1662,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118420824</v>
+        <v>118420490</v>
       </c>
       <c r="B11" t="n">
-        <v>78228</v>
+        <v>90437</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1709,21 +1678,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>3242</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1733,10 +1702,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>388469</v>
+        <v>388468</v>
       </c>
       <c r="R11" t="n">
-        <v>6844519</v>
+        <v>6844616</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1779,6 +1748,26 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1795,10 +1784,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118418878</v>
+        <v>118420637</v>
       </c>
       <c r="B12" t="n">
-        <v>79109</v>
+        <v>100131</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1807,38 +1796,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>1853</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mosippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pulsatilla vernalis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Västanberget (Västanberget), Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>388660</v>
+        <v>388471</v>
       </c>
       <c r="R12" t="n">
-        <v>6844317</v>
+        <v>6844575</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1881,26 +1879,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1917,10 +1895,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118420091</v>
+        <v>118420773</v>
       </c>
       <c r="B13" t="n">
-        <v>78491</v>
+        <v>100131</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1929,25 +1907,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1853</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mosippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pulsatilla vernalis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1957,10 +1935,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>388686</v>
+        <v>388501</v>
       </c>
       <c r="R13" t="n">
-        <v>6844618</v>
+        <v>6844507</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2003,26 +1981,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2039,10 +1997,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118420061</v>
+        <v>118421034</v>
       </c>
       <c r="B14" t="n">
-        <v>78491</v>
+        <v>91786</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2051,25 +2009,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2079,10 +2037,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>388644</v>
+        <v>388505</v>
       </c>
       <c r="R14" t="n">
-        <v>6844604</v>
+        <v>6844252</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2125,26 +2083,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2263,10 +2201,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118420637</v>
+        <v>118420182</v>
       </c>
       <c r="B16" t="n">
-        <v>100131</v>
+        <v>78491</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2275,47 +2213,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1853</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mosippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pulsatilla vernalis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Västanberget (Västanberget), Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>388471</v>
+        <v>388647</v>
       </c>
       <c r="R16" t="n">
-        <v>6844575</v>
+        <v>6844639</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2358,6 +2287,26 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2374,10 +2323,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118419458</v>
+        <v>118418584</v>
       </c>
       <c r="B17" t="n">
-        <v>79109</v>
+        <v>90661</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2386,25 +2335,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2414,10 +2363,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>388790</v>
+        <v>388595</v>
       </c>
       <c r="R17" t="n">
-        <v>6844263</v>
+        <v>6844385</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2460,6 +2409,26 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2476,10 +2445,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118419164</v>
+        <v>118419412</v>
       </c>
       <c r="B18" t="n">
-        <v>79109</v>
+        <v>78491</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2492,21 +2461,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2516,10 +2485,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>388677</v>
+        <v>388803</v>
       </c>
       <c r="R18" t="n">
-        <v>6844240</v>
+        <v>6844256</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2562,6 +2531,26 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2578,7 +2567,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118420275</v>
+        <v>118420091</v>
       </c>
       <c r="B19" t="n">
         <v>78491</v>
@@ -2618,10 +2607,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>388584</v>
+        <v>388686</v>
       </c>
       <c r="R19" t="n">
-        <v>6844653</v>
+        <v>6844618</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2667,22 +2656,22 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2700,10 +2689,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118420723</v>
+        <v>118420814</v>
       </c>
       <c r="B20" t="n">
-        <v>100131</v>
+        <v>78227</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2712,47 +2701,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1853</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mosippa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pulsatilla vernalis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Västanberget (Västanberget), Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>388503</v>
+        <v>388469</v>
       </c>
       <c r="R20" t="n">
-        <v>6844553</v>
+        <v>6844519</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2811,10 +2791,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118420490</v>
+        <v>118420061</v>
       </c>
       <c r="B21" t="n">
-        <v>90437</v>
+        <v>78491</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2827,21 +2807,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3242</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2851,10 +2831,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>388468</v>
+        <v>388644</v>
       </c>
       <c r="R21" t="n">
-        <v>6844616</v>
+        <v>6844604</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2910,12 +2890,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Pinus sylvestris</t>
+          <t>Branch on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3035,10 +3015,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118419050</v>
+        <v>118419640</v>
       </c>
       <c r="B23" t="n">
-        <v>100131</v>
+        <v>79080</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3047,25 +3027,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1853</v>
+        <v>229821</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mosippa</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pulsatilla vernalis</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3075,10 +3055,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>388692</v>
+        <v>388768</v>
       </c>
       <c r="R23" t="n">
-        <v>6844280</v>
+        <v>6844285</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3121,6 +3101,26 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3137,10 +3137,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118420560</v>
+        <v>118419304</v>
       </c>
       <c r="B24" t="n">
-        <v>78227</v>
+        <v>95401</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3153,21 +3153,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>53</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3177,10 +3177,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>388466</v>
+        <v>388802</v>
       </c>
       <c r="R24" t="n">
-        <v>6844600</v>
+        <v>6844204</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3239,10 +3239,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118420814</v>
+        <v>118418878</v>
       </c>
       <c r="B25" t="n">
-        <v>78227</v>
+        <v>79109</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3255,21 +3255,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3279,10 +3279,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>388469</v>
+        <v>388660</v>
       </c>
       <c r="R25" t="n">
-        <v>6844519</v>
+        <v>6844317</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3325,6 +3325,26 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3341,10 +3361,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118420695</v>
+        <v>118420560</v>
       </c>
       <c r="B26" t="n">
-        <v>100131</v>
+        <v>78227</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3353,25 +3373,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1853</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mosippa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pulsatilla vernalis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3381,10 +3401,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>388483</v>
+        <v>388466</v>
       </c>
       <c r="R26" t="n">
-        <v>6844565</v>
+        <v>6844600</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3443,10 +3463,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118420972</v>
+        <v>118420824</v>
       </c>
       <c r="B27" t="n">
-        <v>79080</v>
+        <v>78228</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3459,21 +3479,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3545,10 +3565,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118420773</v>
+        <v>118419458</v>
       </c>
       <c r="B28" t="n">
-        <v>100131</v>
+        <v>79109</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3557,25 +3577,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1853</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mosippa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pulsatilla vernalis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3585,10 +3605,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>388501</v>
+        <v>388790</v>
       </c>
       <c r="R28" t="n">
-        <v>6844507</v>
+        <v>6844263</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3647,10 +3667,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118419451</v>
+        <v>118419050</v>
       </c>
       <c r="B29" t="n">
-        <v>78227</v>
+        <v>100131</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3659,25 +3679,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>1853</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mosippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Pulsatilla vernalis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3687,10 +3707,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>388790</v>
+        <v>388692</v>
       </c>
       <c r="R29" t="n">
-        <v>6844263</v>
+        <v>6844280</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3749,10 +3769,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118418751</v>
+        <v>118419451</v>
       </c>
       <c r="B30" t="n">
-        <v>95401</v>
+        <v>78227</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3765,21 +3785,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>53</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3789,10 +3809,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>388594</v>
+        <v>388790</v>
       </c>
       <c r="R30" t="n">
-        <v>6844349</v>
+        <v>6844263</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3835,26 +3855,6 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
